--- a/Extracted_data_analysis/polar/Output-Transformed_data/sampling_unit_tot.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/sampling_unit_tot.xlsx
@@ -41,16 +41,16 @@
     <t xml:space="preserve">transect</t>
   </si>
   <si>
+    <t xml:space="preserve">Sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stationary</t>
   </si>
   <si>
     <t xml:space="preserve">stationary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample</t>
   </si>
   <si>
     <t xml:space="preserve">Experimental unit</t>
@@ -404,7 +404,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -437,7 +437,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +448,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
